--- a/Selena_Legacy_Data_INITIAL.xlsx
+++ b/Selena_Legacy_Data_INITIAL.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5378173892334</v>
+        <v>8752167857609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,17 +486,13 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1000.pdf</t>
-        </is>
-      </c>
+          <t>28 kg/m3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -508,11 +504,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6344133179342</v>
+        <v>4236057267565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -521,7 +517,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +527,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -543,20 +539,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
+          <t>Mousse Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8874326971831</v>
+        <v>2893065528455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -578,20 +574,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9782657883637</v>
+        <v>4760793164326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20 kg/m3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -613,23 +609,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4464281762099</v>
+        <v>2052524886138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1004.pdf</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -644,26 +644,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Artelit Silikon Sanitarny</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8022669861656</v>
+        <v>1794234331021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -675,20 +675,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
+          <t>Mousse Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3952031874881</v>
+        <v>3607094219856</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -710,20 +710,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3714633034243</v>
+        <v>8263639919343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30 kg/m3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -749,19 +749,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7163018941571</v>
+        <v>2927062980266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1008.pdf</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -776,11 +780,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3188569644058</v>
+        <v>2183419236281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -799,7 +803,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -811,20 +815,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5378173892334</v>
+        <v>8752167857609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27 kg/m3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -846,20 +850,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6344133179342</v>
+        <v>4236057267565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26 kg/m3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -869,7 +873,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -881,11 +885,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8874326971831</v>
+        <v>2893065528455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -894,17 +898,13 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1012.pdf</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -916,11 +916,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL KLEJ FIX2  </t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9782657883637</v>
+        <v>4760793164326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -951,26 +951,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4464281762099</v>
+        <v>2052524886138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1014.pdf</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -982,11 +986,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8022669861656</v>
+        <v>1794234331021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -995,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1017,20 +1021,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mousse Artelit Klej Fix2</t>
+          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3952031874881</v>
+        <v>3607094219856</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30 kg/m3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1052,20 +1056,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3714633034243</v>
+        <v>8263639919343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1075,7 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1087,11 +1091,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7163018941571</v>
+        <v>2927062980266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1100,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1122,30 +1126,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3188569644058</v>
+        <v>2183419236281</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1019.pdf</t>
-        </is>
-      </c>
+          <t>23 kg/m3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1157,11 +1157,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL KLEJ FIX2  </t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1058682193445</v>
+        <v>4463282966117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1192,20 +1192,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8715117804382</v>
+        <v>5719895208452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27 kg/m3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1227,20 +1227,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6294075288079</v>
+        <v>3014909833096</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1266,19 +1266,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9186185848502</v>
+        <v>6464571224759</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1023.pdf</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -1293,20 +1297,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7467004618155</v>
+        <v>4924751211578</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1316,7 +1320,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1328,20 +1332,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Mousse Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8344590585850</v>
+        <v>8498444065138</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23 kg/m3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1351,7 +1355,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1363,20 +1367,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4876766323931</v>
+        <v>6846915783781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1386,7 +1390,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1398,20 +1402,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Mousse Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5830751435166</v>
+        <v>3018667068236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1433,11 +1437,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2541921310761</v>
+        <v>8088745651215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1446,7 +1450,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1456,7 +1460,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1472,26 +1476,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1837640308343</v>
+        <v>6399406808684</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1029.pdf</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1503,26 +1503,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5805160588911</v>
+        <v>6903577573831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22 kg/m3</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1030.pdf</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1534,11 +1538,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3366858305704</v>
+        <v>9372306162861</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1547,14 +1551,10 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1031.pdf</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -1569,27 +1569,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3050134715475</v>
+        <v>9426646806022</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1032.pdf</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -1604,20 +1600,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2474868174150</v>
+        <v>4839616754629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1627,7 +1623,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1639,20 +1635,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8719308305932</v>
+        <v>9319236221700</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,20 +1670,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8652016489943</v>
+        <v>1159303068969</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1697,7 +1693,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1709,11 +1705,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT KLEJ FIX2  </t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6431429645315</v>
+        <v>2744460982750</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1722,7 +1718,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1732,7 +1728,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1744,23 +1740,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t xml:space="preserve">  ARTELIT KLEJ FIX2  </t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3331112155758</v>
+        <v>4800217003895</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1037.pdf</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -1775,20 +1775,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3361667826705</v>
+        <v>3399061348419</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1810,20 +1810,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL KLEJ FIX2  </t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2116810251962</v>
+        <v>7351914924233</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1845,20 +1845,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8802480519614</v>
+        <v>8653589174947</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20 kg/m3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1880,11 +1880,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4216677327882</v>
+        <v>7975992297811</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1893,13 +1893,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1041.pdf</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1911,26 +1915,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3065589789922</v>
+        <v>1105727333904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>27 kg/m3</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1042.pdf</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1942,26 +1950,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Mousse Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6581815589425</v>
+        <v>6578536710611</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>28 kg/m3</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1043.pdf</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1973,20 +1985,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4742503550712</v>
+        <v>7649285435337</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2008,20 +2020,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
+          <t>Mousse Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2853343938704</v>
+        <v>7937353461559</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2031,7 +2043,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2043,20 +2055,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3530186665272</v>
+        <v>2254382474668</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20 kg/m3</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2066,7 +2078,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2078,30 +2090,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4725877341208</v>
+        <v>9500885725153</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1047.pdf</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2113,11 +2121,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8650771138981</v>
+        <v>2259602564922</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2126,7 +2134,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2148,20 +2156,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL KLEJ FIX2  </t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3356783066634</v>
+        <v>8837124382189</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26 kg/m3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2171,7 +2179,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2183,20 +2191,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mousse Artelit Klej Fix2</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8057008990008</v>
+        <v>6093257624840</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2206,7 +2214,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2218,30 +2226,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6649578408106</v>
+        <v>7270011574069</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1051.pdf</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2253,20 +2257,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Mousse Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6968733837222</v>
+        <v>4260718493008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30 kg/m3</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2276,7 +2280,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2288,20 +2292,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Mousse Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4772614139806</v>
+        <v>7659662268714</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20 kg/m3</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2323,20 +2327,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1052861387752</v>
+        <v>4410489689561</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>22 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2346,7 +2350,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2358,30 +2362,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1713903214243</v>
+        <v>1683510298692</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1055.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2393,20 +2393,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5551603476820</v>
+        <v>6128870282327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2428,11 +2428,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5228798387520</v>
+        <v>4128268616743</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>30 kg/m3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2463,11 +2463,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2238053637585</v>
+        <v>9081504056920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2498,11 +2498,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2443394692443</v>
+        <v>2680924202250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2533,20 +2533,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5755215257448</v>
+        <v>5110033164827</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2568,20 +2568,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5149976668305</v>
+        <v>6359727781882</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2603,20 +2603,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7057236931336</v>
+        <v>2524834292213</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5275353238340</v>
+        <v>2132634819632</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2651,10 +2651,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1063.pdf</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -2669,20 +2673,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5665322955372</v>
+        <v>3210042484187</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>27 kg/m3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2692,7 +2696,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2704,20 +2708,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t>Mousse Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9487213773352</v>
+        <v>2101843653145</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2727,7 +2731,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2739,20 +2743,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9518883419314</v>
+        <v>7153037182316</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2774,20 +2778,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Mousse Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5134123813034</v>
+        <v>1963951178364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>24 kg/m3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2797,7 +2801,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2809,20 +2813,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3334083932806</v>
+        <v>5582183398205</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2844,26 +2848,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4709523457654</v>
+        <v>6613038399494</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1069.pdf</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2875,20 +2883,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9954571394313</v>
+        <v>1628035620799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2898,7 +2906,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2910,30 +2918,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1400634430439</v>
+        <v>3503560136682</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1071.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2945,26 +2949,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8643019841877</v>
+        <v>5319581949455</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1072.pdf</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2976,11 +2984,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6935206188161</v>
+        <v>9890039511679</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2992,11 +3000,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1073.pdf</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -3011,20 +3015,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8482267920027</v>
+        <v>9191829276099</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3034,7 +3038,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3046,20 +3050,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Mousse Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6966242242365</v>
+        <v>1049794663708</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22 kg/m3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3069,7 +3073,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3081,20 +3085,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL KLEJ FIX2  </t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6776967111397</v>
+        <v>9403942692974</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3116,20 +3120,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1662109815000</v>
+        <v>7428925382389</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20 kg/m3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3151,11 +3155,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9300943099236</v>
+        <v>5861090712118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3174,7 +3178,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3186,20 +3190,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7125641250587</v>
+        <v>9851835131072</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3209,7 +3213,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3221,11 +3225,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6781413762218</v>
+        <v>2555872688129</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3234,10 +3238,14 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1080.pdf</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -3252,20 +3260,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2749732278057</v>
+        <v>4345790925489</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3287,11 +3295,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6820594845002</v>
+        <v>7452563170336</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3300,7 +3308,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3310,7 +3318,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3322,20 +3330,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2833514552515</v>
+        <v>4805814994799</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>26 kg/m3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3345,7 +3353,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3357,20 +3365,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8352411674492</v>
+        <v>9758501126444</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3380,7 +3388,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3392,26 +3400,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Mousse Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5855686951890</v>
+        <v>5879050548824</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>21 kg/m3</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1085.pdf</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3423,11 +3435,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6046014870937</v>
+        <v>3370951422097</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3436,7 +3448,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3446,7 +3458,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3458,26 +3470,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1742148559995</v>
+        <v>1248573528685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>28 kg/m3</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1087.pdf</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3489,26 +3505,30 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Artelit Silikon Sanitarny</t>
+          <t>Mousse Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7227672436686</v>
+        <v>1085330683268</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>23 kg/m3</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1088.pdf</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3520,20 +3540,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4510330412869</v>
+        <v>1522465041489</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3543,7 +3563,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3555,20 +3575,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4753403689072</v>
+        <v>2873432149063</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23 kg/m3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3578,7 +3598,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3590,20 +3610,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2423614829520</v>
+        <v>6301242150038</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3613,7 +3633,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3625,20 +3645,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mousse Artelit Klej Fix2</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9321360945847</v>
+        <v>7096109238311</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3648,7 +3668,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3660,11 +3680,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5880454997974</v>
+        <v>3124395641265</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3673,7 +3693,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3683,7 +3703,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3695,11 +3715,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Mousse Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5810562694186</v>
+        <v>8271954408988</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3708,7 +3728,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>29 kg/m3</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3718,7 +3738,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3730,26 +3750,30 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5712161193508</v>
+        <v>4202042993337</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1095.pdf</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3761,11 +3785,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>7940081444587</v>
+        <v>6530875644106</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3774,7 +3798,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3784,7 +3808,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3796,20 +3820,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3287800277732</v>
+        <v>3828039096400</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3831,30 +3855,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>8522059501608</v>
+        <v>4485357398066</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1098.pdf</t>
-        </is>
-      </c>
+          <t>24 kg/m3</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3866,20 +3886,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2618558137840</v>
+        <v>6372752264093</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3889,7 +3909,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>

--- a/Selena_Legacy_Data_INITIAL.xlsx
+++ b/Selena_Legacy_Data_INITIAL.xlsx
@@ -473,26 +473,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8752167857609</v>
+        <v>1936449043351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1000.pdf</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -504,30 +508,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4236057267565</v>
+        <v>1936449043351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1001.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -539,20 +539,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2893065528455</v>
+        <v>8581718461680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -574,30 +574,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4760793164326</v>
+        <v>8581718461680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1003.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -609,11 +605,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2052524886138</v>
+        <v>9886971264575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -622,7 +618,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -632,7 +628,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -644,26 +640,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1794234331021</v>
+        <v>9886971264575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -675,20 +671,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3607094219856</v>
+        <v>6762341715348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -698,7 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -710,30 +706,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8263639919343</v>
+        <v>6762341715348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1007.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -745,11 +737,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2927062980266</v>
+        <v>1791623521699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -758,7 +750,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -768,7 +760,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -780,30 +772,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2183419236281</v>
+        <v>1791623521699</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1009.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -815,20 +803,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8752167857609</v>
+        <v>7450121326874</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27 kg/m3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -838,7 +826,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -850,11 +838,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4236057267565</v>
+        <v>7450121326874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -863,14 +851,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26 kg/m3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1011.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Unmapped_FR</t>
@@ -889,7 +873,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2893065528455</v>
+        <v>6855268434259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -901,10 +885,14 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-1012.pdf</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -916,30 +904,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4760793164326</v>
+        <v>6855268434259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1013.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -951,20 +935,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2052524886138</v>
+        <v>2097253614102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -974,7 +958,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -986,30 +970,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Artelit Silikon Sanitarny</t>
+          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1794234331021</v>
+        <v>2097253614102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1015.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1021,20 +1001,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3607094219856</v>
+        <v>1677703171119</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,7 +1024,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1056,30 +1036,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8263639919343</v>
+        <v>1677703171119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1017.pdf</t>
-        </is>
-      </c>
+          <t>25 kg/m3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1091,11 +1067,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2927062980266</v>
+        <v>9158789111331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1104,7 +1080,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,7 +1090,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1126,11 +1102,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2183419236281</v>
+        <v>9158789111331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1139,7 +1115,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>23 kg/m3</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1152,30 +1128,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEL-1020</t>
+          <t>SEL-2010</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4463282966117</v>
+        <v>1204110767442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1020.pdf</t>
+          <t>https://selena.com/msds/SEL-2010.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1187,51 +1163,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEL-1021</t>
+          <t>SEL-2011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5719895208452</v>
+        <v>1431313708027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>27 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1021.pdf</t>
+          <t>https://selena.com/msds/SEL-2011.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEL-1022</t>
+          <t>SEL-2012</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3014909833096</v>
+        <v>8186927286505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1240,33 +1216,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1022.pdf</t>
+          <t>https://selena.com/msds/SEL-2012.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEL-1023</t>
+          <t>SEL-2013</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6464571224759</v>
+        <v>3795160531739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1275,117 +1251,113 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1023.pdf</t>
+          <t>https://selena.com/msds/SEL-2013.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEL-1024</t>
+          <t>SEL-2014</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4924751211578</v>
+        <v>6446862466631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1024.pdf</t>
+          <t>https://selena.com/msds/SEL-2014.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEL-1025</t>
+          <t>SEL-2015</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8498444065138</v>
+        <v>4513340336745</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23 kg/m3</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1025.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEL-1026</t>
+          <t>SEL-2016</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6846915783781</v>
+        <v>5213263670202</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1026.pdf</t>
+          <t>https://selena.com/msds/SEL-2016.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1397,51 +1369,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEL-1027</t>
+          <t>SEL-2017</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3018667068236</v>
+        <v>8876000680564</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1027.pdf</t>
+          <t>https://selena.com/msds/SEL-2017.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEL-1028</t>
+          <t>SEL-2018</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8088745651215</v>
+        <v>2460088159013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1450,111 +1422,119 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1028.pdf</t>
+          <t>https://selena.com/msds/SEL-2018.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEL-1029</t>
+          <t>SEL-2019</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6399406808684</v>
+        <v>5988931325193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2019.pdf</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEL-1030</t>
+          <t>SEL-2020</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6903577573831</v>
+        <v>4380545170318</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1030.pdf</t>
+          <t>https://selena.com/msds/SEL-2020.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEL-1031</t>
+          <t>SEL-2021</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9372306162861</v>
+        <v>2422334086189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2021.pdf</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -1564,16 +1544,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEL-1032</t>
+          <t>SEL-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9426646806022</v>
+        <v>3989697366878</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1582,10 +1562,14 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2022.pdf</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -1595,65 +1579,65 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEL-1033</t>
+          <t>SEL-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT PIANA 65  </t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4839616754629</v>
+        <v>6023232068164</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1033.pdf</t>
+          <t>https://selena.com/msds/SEL-2023.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEL-1034</t>
+          <t>SEL-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9319236221700</v>
+        <v>2684136327243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1034.pdf</t>
+          <t>https://selena.com/msds/SEL-2024.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1665,16 +1649,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEL-1035</t>
+          <t>SEL-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1159303068969</v>
+        <v>9978197023914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1683,12 +1667,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1035.pdf</t>
+          <t>https://selena.com/msds/SEL-2025.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1700,30 +1684,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEL-1036</t>
+          <t>SEL-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2744460982750</v>
+        <v>4102374178177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1036.pdf</t>
+          <t>https://selena.com/msds/SEL-2026.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1735,51 +1719,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEL-1037</t>
+          <t>SEL-2027</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT KLEJ FIX2  </t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4800217003895</v>
+        <v>4573368667749</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1037.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEL-1038</t>
+          <t>SEL-2028</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3399061348419</v>
+        <v>3934611066963</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1788,33 +1768,33 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1038.pdf</t>
+          <t>https://selena.com/msds/SEL-2028.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEL-1039</t>
+          <t>SEL-2029</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7351914924233</v>
+        <v>2734724082384</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1823,33 +1803,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1039.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEL-1040</t>
+          <t>SEL-2030</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8653589174947</v>
+        <v>8073847124972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1858,12 +1834,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1040.pdf</t>
+          <t>https://selena.com/msds/SEL-2030.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1875,16 +1851,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEL-1041</t>
+          <t>SEL-2031</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7975992297811</v>
+        <v>9849521365811</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1893,12 +1869,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1041.pdf</t>
+          <t>https://selena.com/msds/SEL-2031.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1910,51 +1886,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEL-1042</t>
+          <t>SEL-2032</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1105727333904</v>
+        <v>3614691233930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>27 kg/m3</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1042.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEL-1043</t>
+          <t>SEL-2033</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6578536710611</v>
+        <v>5029944637928</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1963,12 +1935,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1043.pdf</t>
+          <t>https://selena.com/msds/SEL-2033.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1980,30 +1952,30 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEL-1044</t>
+          <t>SEL-2034</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7649285435337</v>
+        <v>2670068131331</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1044.pdf</t>
+          <t>https://selena.com/msds/SEL-2034.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2015,187 +1987,187 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEL-1045</t>
+          <t>SEL-2035</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7937353461559</v>
+        <v>6262788108202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1045.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEL-1046</t>
+          <t>SEL-2036</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2254382474668</v>
+        <v>3118512000486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1046.pdf</t>
+          <t>https://selena.com/msds/SEL-2036.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEL-1047</t>
+          <t>SEL-2037</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9500885725153</v>
+        <v>8974913206818</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2037.pdf</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEL-1048</t>
+          <t>SEL-2038</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2259602564922</v>
+        <v>1490743066339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1048.pdf</t>
+          <t>https://selena.com/msds/SEL-2038.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEL-1049</t>
+          <t>SEL-2039</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8837124382189</v>
+        <v>7891987761138</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1049.pdf</t>
+          <t>https://selena.com/msds/SEL-2039.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEL-1050</t>
+          <t>SEL-2040</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6093257624840</v>
+        <v>9639993111258</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2204,134 +2176,134 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1050.pdf</t>
+          <t>https://selena.com/msds/SEL-2040.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEL-1051</t>
+          <t>SEL-2041</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL PIANA 65  </t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7270011574069</v>
+        <v>7932569138128</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEL-1052</t>
+          <t>SEL-2042</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4260718493008</v>
+        <v>4684061093349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>30 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1052.pdf</t>
+          <t>https://selena.com/msds/SEL-2042.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEL-1053</t>
+          <t>SEL-2043</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7659662268714</v>
+        <v>9891607373060</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1053.pdf</t>
+          <t>https://selena.com/msds/SEL-2043.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEL-1054</t>
+          <t>SEL-2044</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4410489689561</v>
+        <v>1092684287836</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2340,37 +2312,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1054.pdf</t>
+          <t>https://selena.com/msds/SEL-2044.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEL-1055</t>
+          <t>SEL-2045</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1683510298692</v>
+        <v>2456811561472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2378,61 +2350,65 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2045.pdf</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEL-1056</t>
+          <t>SEL-2046</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6128870282327</v>
+        <v>5137387139033</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1056.pdf</t>
+          <t>https://selena.com/msds/SEL-2046.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEL-1057</t>
+          <t>SEL-2047</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4128268616743</v>
+        <v>1791439611947</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2441,12 +2417,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>30 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1057.pdf</t>
+          <t>https://selena.com/msds/SEL-2047.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2458,121 +2434,117 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEL-1058</t>
+          <t>SEL-2048</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA KLEJ FIX2  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9081504056920</v>
+        <v>1022373185644</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1058.pdf</t>
+          <t>https://selena.com/msds/SEL-2048.pdf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEL-1059</t>
+          <t>SEL-2049</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2680924202250</v>
+        <v>6715757390739</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1059.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEL-1060</t>
+          <t>SEL-2050</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5110033164827</v>
+        <v>6173511481463</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1060.pdf</t>
+          <t>https://selena.com/msds/SEL-2050.pdf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEL-1061</t>
+          <t>SEL-2051</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6359727781882</v>
+        <v>3441744655831</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2581,49 +2553,41 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1061.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEL-1062</t>
+          <t>SEL-2052</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2524834292213</v>
+        <v>3989592443173</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1062.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -2633,51 +2597,51 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEL-1063</t>
+          <t>SEL-2053</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2132634819632</v>
+        <v>3197400489411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1063.pdf</t>
+          <t>https://selena.com/msds/SEL-2053.pdf</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEL-1064</t>
+          <t>SEL-2054</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3210042484187</v>
+        <v>7292520518128</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2686,12 +2650,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1064.pdf</t>
+          <t>https://selena.com/msds/SEL-2054.pdf</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2703,51 +2667,51 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEL-1065</t>
+          <t>SEL-2055</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2101843653145</v>
+        <v>5926862184008</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1065.pdf</t>
+          <t>https://selena.com/msds/SEL-2055.pdf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEL-1066</t>
+          <t>SEL-2056</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7153037182316</v>
+        <v>3925124752011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2756,33 +2720,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1066.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEL-1067</t>
+          <t>SEL-2057</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1963951178364</v>
+        <v>3779377392144</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2791,12 +2751,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1067.pdf</t>
+          <t>https://selena.com/msds/SEL-2057.pdf</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2808,125 +2768,121 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEL-1068</t>
+          <t>SEL-2058</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5582183398205</v>
+        <v>9299038180693</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1068.pdf</t>
+          <t>https://selena.com/msds/SEL-2058.pdf</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEL-1069</t>
+          <t>SEL-2059</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6613038399494</v>
+        <v>6618629275523</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1069.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEL-1070</t>
+          <t>SEL-2060</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1628035620799</v>
+        <v>1724818207492</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1070.pdf</t>
+          <t>https://selena.com/msds/SEL-2060.pdf</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEL-1071</t>
+          <t>SEL-2061</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3503560136682</v>
+        <v>6311693356798</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2937,23 +2893,23 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEL-1072</t>
+          <t>SEL-2062</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5319581949455</v>
+        <v>8968221113311</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2962,64 +2918,64 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1072.pdf</t>
+          <t>https://selena.com/msds/SEL-2062.pdf</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEL-1073</t>
+          <t>SEL-2063</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9890039511679</v>
+        <v>1764984288667</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEL-1074</t>
+          <t>SEL-2064</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9191829276099</v>
+        <v>9090418529904</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3028,12 +2984,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1074.pdf</t>
+          <t>https://selena.com/msds/SEL-2064.pdf</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3045,16 +3001,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEL-1075</t>
+          <t>SEL-2065</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1049794663708</v>
+        <v>3726173435905</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3063,12 +3019,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1075.pdf</t>
+          <t>https://selena.com/msds/SEL-2065.pdf</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3080,16 +3036,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEL-1076</t>
+          <t>SEL-2066</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9403942692974</v>
+        <v>6580952323893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3098,103 +3054,91 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1076.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEL-1077</t>
+          <t>SEL-2067</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7428925382389</v>
+        <v>4992598590558</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1077.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEL-1078</t>
+          <t>SEL-2068</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5861090712118</v>
+        <v>2343285886804</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1078.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEL-1079</t>
+          <t>SEL-2069</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TYTAN PROFESSIONAL SILIKON SANITARNY  </t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9851835131072</v>
+        <v>6672228217380</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3203,68 +3147,64 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1079.pdf</t>
+          <t>https://selena.com/msds/SEL-2069.pdf</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEL-1080</t>
+          <t>SEL-2070</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2555872688129</v>
+        <v>1832833357240</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1080.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SEL-1081</t>
+          <t>SEL-2071</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4345790925489</v>
+        <v>8574279730643</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3273,12 +3213,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1081.pdf</t>
+          <t>https://selena.com/msds/SEL-2071.pdf</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3290,16 +3230,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SEL-1082</t>
+          <t>SEL-2072</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7452563170336</v>
+        <v>6450486585484</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3308,68 +3248,68 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1082.pdf</t>
+          <t>https://selena.com/msds/SEL-2072.pdf</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SEL-1083</t>
+          <t>SEL-2073</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4805814994799</v>
+        <v>9616763618027</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1083.pdf</t>
+          <t>https://selena.com/msds/SEL-2073.pdf</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SEL-1084</t>
+          <t>SEL-2074</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9758501126444</v>
+        <v>7683489560336</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3378,12 +3318,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1084.pdf</t>
+          <t>https://selena.com/msds/SEL-2074.pdf</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3395,51 +3335,51 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEL-1085</t>
+          <t>SEL-2075</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5879050548824</v>
+        <v>9673000607724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1085.pdf</t>
+          <t>https://selena.com/msds/SEL-2075.pdf</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEL-1086</t>
+          <t>SEL-2076</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA PIANA 65  </t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3370951422097</v>
+        <v>2745092225361</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3448,12 +3388,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1086.pdf</t>
+          <t>https://selena.com/msds/SEL-2076.pdf</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3465,86 +3405,86 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SEL-1087</t>
+          <t>SEL-2077</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1248573528685</v>
+        <v>5303184181413</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1087.pdf</t>
+          <t>https://selena.com/msds/SEL-2077.pdf</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SEL-1088</t>
+          <t>SEL-2078</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1085330683268</v>
+        <v>9418863880088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>23 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1088.pdf</t>
+          <t>https://selena.com/msds/SEL-2078.pdf</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SEL-1089</t>
+          <t>SEL-2079</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1522465041489</v>
+        <v>7528580919923</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3553,12 +3493,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1089.pdf</t>
+          <t>https://selena.com/msds/SEL-2079.pdf</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3570,55 +3510,55 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SEL-1090</t>
+          <t>SEL-2080</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2873432149063</v>
+        <v>4465563544233</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>23 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1090.pdf</t>
+          <t>https://selena.com/msds/SEL-2080.pdf</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SEL-1091</t>
+          <t>SEL-2081</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUILOSA SILIKON SANITARNY  </t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6301242150038</v>
+        <v>5726340673312</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3628,98 +3568,94 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1091.pdf</t>
+          <t>https://selena.com/msds/SEL-2081.pdf</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SEL-1092</t>
+          <t>SEL-2082</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7096109238311</v>
+        <v>2576561330723</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1092.pdf</t>
+          <t>https://selena.com/msds/SEL-2082.pdf</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SEL-1093</t>
+          <t>SEL-2083</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3124395641265</v>
+        <v>3337387430454</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1093.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SEL-1094</t>
+          <t>SEL-2084</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8271954408988</v>
+        <v>5093439265601</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3728,12 +3664,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1094.pdf</t>
+          <t>https://selena.com/msds/SEL-2084.pdf</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3745,30 +3681,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SEL-1095</t>
+          <t>SEL-2085</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4202042993337</v>
+        <v>1749267817447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1095.pdf</t>
+          <t>https://selena.com/msds/SEL-2085.pdf</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3780,51 +3716,51 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SEL-1096</t>
+          <t>SEL-2086</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6530875644106</v>
+        <v>6718682523145</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1096.pdf</t>
+          <t>https://selena.com/msds/SEL-2086.pdf</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SEL-1097</t>
+          <t>SEL-2087</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ARTELIT SILIKON SANITARNY  </t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3828039096400</v>
+        <v>9582594916875</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3838,78 +3774,78 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1097.pdf</t>
+          <t>https://selena.com/msds/SEL-2087.pdf</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SEL-1098</t>
+          <t>SEL-2088</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4485357398066</v>
+        <v>7856245875389</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2088.pdf</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SEL-1099</t>
+          <t>SEL-2089</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6372752264093</v>
+        <v>1143805552958</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-1099.pdf</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>

--- a/Selena_Legacy_Data_INITIAL.xlsx
+++ b/Selena_Legacy_Data_INITIAL.xlsx
@@ -473,11 +473,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1936449043351</v>
+        <v>1566835332485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,11 +508,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1936449043351</v>
+        <v>1566835332485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -539,11 +539,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8581718461680</v>
+        <v>2994926040090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -574,11 +574,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8581718461680</v>
+        <v>2994926040090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -605,11 +605,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9886971264575</v>
+        <v>9375438373744</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -640,11 +640,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9886971264575</v>
+        <v>9375438373744</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -671,11 +671,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6762341715348</v>
+        <v>5984514376820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6762341715348</v>
+        <v>5984514376820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -737,11 +737,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1791623521699</v>
+        <v>4988388359578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -772,11 +772,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1791623521699</v>
+        <v>4988388359578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7450121326874</v>
+        <v>2111212281929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7450121326874</v>
+        <v>2111212281929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6855268434259</v>
+        <v>6217899904404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -904,11 +904,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6855268434259</v>
+        <v>6217899904404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2097253614102</v>
+        <v>6726448885766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2097253614102</v>
+        <v>6726448885766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1677703171119</v>
+        <v>5680754578052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1677703171119</v>
+        <v>5680754578052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9158789111331</v>
+        <v>3720203329847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1102,11 +1102,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9158789111331</v>
+        <v>3720203329847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1133,15 +1133,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1204110767442</v>
+        <v>5568553532168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1149,14 +1149,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2010.pdf</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1168,15 +1164,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1431313708027</v>
+        <v>2155356418205</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1191,7 +1187,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1203,15 +1199,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8186927286505</v>
+        <v>5557449107777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1238,11 +1234,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3795160531739</v>
+        <v>5316895966439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1254,11 +1250,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2013.pdf</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Piany</t>
@@ -1273,15 +1265,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6446862466631</v>
+        <v>3742388369829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1296,7 +1288,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1304,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4513340336745</v>
+        <v>9258849173192</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1324,7 +1316,11 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2015.pdf</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Piany</t>
@@ -1339,15 +1335,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5213263670202</v>
+        <v>1196335157919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1355,14 +1351,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2016.pdf</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1374,15 +1366,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8876000680564</v>
+        <v>1549660764440</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1397,7 +1389,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1405,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2460088159013</v>
+        <v>5589144525338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1432,7 +1424,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1444,15 +1436,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5988931325193</v>
+        <v>8952056783141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1467,7 +1459,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1479,15 +1471,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4380545170318</v>
+        <v>8133649473488</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1502,7 +1494,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1514,15 +1506,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2422334086189</v>
+        <v>1103460358158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1553,7 +1545,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3989697366878</v>
+        <v>5683540147917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1572,7 +1564,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1584,15 +1576,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6023232068164</v>
+        <v>9615235218192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1607,7 +1599,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1619,15 +1611,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2684136327243</v>
+        <v>2317426766374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1642,7 +1634,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1654,11 +1646,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9978197023914</v>
+        <v>2949050357545</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1677,7 +1669,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1693,11 +1685,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4102374178177</v>
+        <v>2990734844744</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1712,7 +1704,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1728,11 +1720,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4573368667749</v>
+        <v>9069208405843</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1740,10 +1732,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2027.pdf</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1755,15 +1751,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3934611066963</v>
+        <v>4655772146290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1778,7 +1774,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1790,11 +1786,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2734724082384</v>
+        <v>2569965626701</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1806,10 +1802,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2029.pdf</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1821,15 +1821,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8073847124972</v>
+        <v>9985701383099</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1856,15 +1856,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9849521365811</v>
+        <v>5196416729763</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1872,14 +1872,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2031.pdf</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1891,11 +1887,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3614691233930</v>
+        <v>1802899632741</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1907,10 +1903,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2032.pdf</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1922,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5029944637928</v>
+        <v>6753028111049</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1957,15 +1957,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2670068131331</v>
+        <v>8533884398650</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1996,11 +1996,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6262788108202</v>
+        <v>6211073899534</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2008,10 +2008,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2035.pdf</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2023,15 +2027,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3118512000486</v>
+        <v>9769784542987</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2046,7 +2050,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2058,11 +2062,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8974913206818</v>
+        <v>2450112974353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2093,11 +2097,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1490743066339</v>
+        <v>1243838531654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2128,15 +2132,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7891987761138</v>
+        <v>7400664031629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2144,14 +2148,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2039.pdf</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2163,15 +2163,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9639993111258</v>
+        <v>6944802264602</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7932569138128</v>
+        <v>1230591513501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2214,10 +2214,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2041.pdf</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2229,15 +2233,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4684061093349</v>
+        <v>4749470651030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2252,7 +2256,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2272,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9891607373060</v>
+        <v>5327123197532</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2280,14 +2284,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2043.pdf</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1092684287836</v>
+        <v>6427847841811</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2334,15 +2334,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2456811561472</v>
+        <v>5554714254640</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2369,15 +2369,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5137387139033</v>
+        <v>8490943567226</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2408,11 +2408,11 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1791439611947</v>
+        <v>4904719933178</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2439,15 +2439,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1022373185644</v>
+        <v>5835814896307</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2474,11 +2474,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6715757390739</v>
+        <v>1067331036573</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2490,7 +2490,11 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2049.pdf</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>Unmapped_FR</t>
@@ -2505,11 +2509,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6173511481463</v>
+        <v>9514284645910</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2528,7 +2532,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2540,15 +2544,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3441744655831</v>
+        <v>3050043884105</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2556,10 +2560,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2051.pdf</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2571,11 +2579,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3989592443173</v>
+        <v>9215430246676</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2587,10 +2595,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2052.pdf</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2602,15 +2614,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3197400489411</v>
+        <v>1136031973805</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2625,7 +2637,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2637,15 +2649,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7292520518128</v>
+        <v>3340641419007</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2653,14 +2665,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2054.pdf</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2684,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5926862184008</v>
+        <v>5913382371158</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2688,14 +2696,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2055.pdf</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2707,11 +2711,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3925124752011</v>
+        <v>5685448258401</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2742,11 +2746,11 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3779377392144</v>
+        <v>3195125652427</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2761,7 +2765,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2773,15 +2777,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9299038180693</v>
+        <v>7505025821971</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2796,7 +2800,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2808,15 +2812,15 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6618629275523</v>
+        <v>8571767709710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2824,7 +2828,11 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2059.pdf</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>Piany</t>
@@ -2839,11 +2847,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1724818207492</v>
+        <v>9857812487029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -2874,15 +2882,15 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6311693356798</v>
+        <v>6952199937048</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2890,10 +2898,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2061.pdf</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2905,11 +2917,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8968221113311</v>
+        <v>2464717434805</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2928,7 +2940,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2940,11 +2952,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1764984288667</v>
+        <v>4853277110507</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2971,15 +2983,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9090418529904</v>
+        <v>6474753320680</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2994,7 +3006,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3006,15 +3018,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3726173435905</v>
+        <v>2160350363282</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3029,7 +3041,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3045,11 +3057,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6580952323893</v>
+        <v>5927072229357</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3057,10 +3069,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2066.pdf</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3072,11 +3088,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4992598590558</v>
+        <v>8323399627172</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3088,7 +3104,11 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2067.pdf</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>Unmapped_FR</t>
@@ -3103,15 +3123,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2343285886804</v>
+        <v>1809087148637</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3119,10 +3139,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2068.pdf</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3162,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6672228217380</v>
+        <v>2723130111648</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3157,7 +3181,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3173,11 +3197,11 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1832833357240</v>
+        <v>8446949691121</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3185,10 +3209,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2070.pdf</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3200,11 +3228,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8574279730643</v>
+        <v>8740893454427</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3223,7 +3251,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3235,11 +3263,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6450486585484</v>
+        <v>2688118934900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3251,11 +3279,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2072.pdf</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>Piany</t>
@@ -3274,7 +3298,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9616763618027</v>
+        <v>8464260157531</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3293,7 +3317,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3305,11 +3329,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7683489560336</v>
+        <v>5930030504103</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3328,7 +3352,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3340,15 +3364,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9673000607724</v>
+        <v>2504852477662</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3363,7 +3387,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3375,15 +3399,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2745092225361</v>
+        <v>7603388086981</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3398,7 +3422,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3410,11 +3434,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5303184181413</v>
+        <v>5287154460207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3445,15 +3469,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9418863880088</v>
+        <v>5243323466939</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3480,15 +3504,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7528580919923</v>
+        <v>5621404241474</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3503,7 +3527,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3515,15 +3539,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4465563544233</v>
+        <v>5055419624749</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3538,7 +3562,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3578,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5726340673312</v>
+        <v>3889017888037</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3585,15 +3609,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2576561330723</v>
+        <v>6476444511735</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3608,7 +3632,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3624,11 +3648,11 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3337387430454</v>
+        <v>9084000269773</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3636,10 +3660,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2083.pdf</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3651,15 +3679,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5093439265601</v>
+        <v>9497169064800</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3667,14 +3695,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2084.pdf</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3686,15 +3710,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1749267817447</v>
+        <v>1880306093083</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3709,7 +3733,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3721,11 +3745,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6718682523145</v>
+        <v>3043721533278</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3744,7 +3768,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3784,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9582594916875</v>
+        <v>5284960962960</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3791,11 +3815,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7856245875389</v>
+        <v>3549807686591</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3814,7 +3838,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3826,11 +3850,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1143805552958</v>
+        <v>4238586979848</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/Selena_Legacy_Data_INITIAL.xlsx
+++ b/Selena_Legacy_Data_INITIAL.xlsx
@@ -473,11 +473,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1566835332485</v>
+        <v>9931863904797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,11 +508,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1566835332485</v>
+        <v>9931863904797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2994926040090</v>
+        <v>7184046578092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2994926040090</v>
+        <v>7184046578092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9375438373744</v>
+        <v>2974969772071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9375438373744</v>
+        <v>2974969772071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -671,11 +671,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5984514376820</v>
+        <v>7255464486479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -706,11 +706,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5984514376820</v>
+        <v>7255464486479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4988388359578</v>
+        <v>5236601819838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4988388359578</v>
+        <v>5236601819838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -803,11 +803,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2111212281929</v>
+        <v>1835401038310</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -838,11 +838,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2111212281929</v>
+        <v>1835401038310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6217899904404</v>
+        <v>5516795735083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -904,11 +904,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6217899904404</v>
+        <v>5516795735083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6726448885766</v>
+        <v>5240637117122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -970,11 +970,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6726448885766</v>
+        <v>5240637117122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1001,11 +1001,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5680754578052</v>
+        <v>7578248896655</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1036,11 +1036,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Tytan Professional Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5680754578052</v>
+        <v>7578248896655</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3720203329847</v>
+        <v>3272518903253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1102,11 +1102,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65 - DUPLIKAT SYSTEMOWY</t>
+          <t>Artelit Piana 65 - DUPLIKAT SYSTEMOWY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3720203329847</v>
+        <v>3272518903253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1137,11 +1137,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5568553532168</v>
+        <v>7152195300055</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1152,7 +1152,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1164,11 +1164,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2155356418205</v>
+        <v>1648236053305</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1199,11 +1199,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5557449107777</v>
+        <v>6344682226985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1215,11 +1215,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2012.pdf</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -1234,15 +1230,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5316895966439</v>
+        <v>9837900690062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1250,10 +1246,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2013.pdf</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1265,15 +1265,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3742388369829</v>
+        <v>4972338655940</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1300,11 +1300,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9258849173192</v>
+        <v>4171446229360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1196335157919</v>
+        <v>9939516610414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1366,15 +1366,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1549660764440</v>
+        <v>5352937446586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1401,15 +1401,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5589144525338</v>
+        <v>7641657459597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1417,14 +1417,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2018.pdf</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1436,15 +1432,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8952056783141</v>
+        <v>7251665745374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1459,7 +1455,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1471,11 +1467,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8133649473488</v>
+        <v>3391053479413</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1510,11 +1506,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1103460358158</v>
+        <v>2906182322287</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1522,14 +1518,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2021.pdf</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1541,15 +1533,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5683540147917</v>
+        <v>7803863049942</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1557,14 +1549,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2022.pdf</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1576,15 +1564,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9615235218192</v>
+        <v>1902392118306</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1599,7 +1587,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1611,15 +1599,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2317426766374</v>
+        <v>2649483799705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1634,7 +1622,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1650,11 +1638,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2949050357545</v>
+        <v>5029983790106</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1669,7 +1657,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1681,11 +1669,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2990734844744</v>
+        <v>1020680633612</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1720,11 +1708,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9069208405843</v>
+        <v>3657429231631</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1739,7 +1727,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1751,11 +1739,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4655772146290</v>
+        <v>6306729292067</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1767,11 +1755,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2028.pdf</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>Unmapped_FR</t>
@@ -1786,11 +1770,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2569965626701</v>
+        <v>6801363462397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1802,14 +1786,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2029.pdf</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1821,15 +1801,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9985701383099</v>
+        <v>9431006780688</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1837,14 +1817,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2030.pdf</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1856,11 +1832,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5196416729763</v>
+        <v>8553095792984</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1872,10 +1848,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2031.pdf</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -1887,11 +1867,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1802899632741</v>
+        <v>8261430870909</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1910,7 +1890,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -1922,15 +1902,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6753028111049</v>
+        <v>1650938104485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1945,7 +1925,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -1957,15 +1937,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8533884398650</v>
+        <v>2333006771293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1973,14 +1953,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2034.pdf</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1972,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6211073899534</v>
+        <v>5956657285554</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2015,7 +1991,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2027,15 +2003,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9769784542987</v>
+        <v>6275662911872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2050,7 +2026,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2062,15 +2038,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2450112974353</v>
+        <v>3575693961882</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2085,7 +2061,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2077,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1243838531654</v>
+        <v>8251623214397</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2113,11 +2089,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2038.pdf</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Unmapped_FR</t>
@@ -2132,15 +2104,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7400664031629</v>
+        <v>6783796336031</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2148,10 +2120,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2039.pdf</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2163,15 +2139,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6944802264602</v>
+        <v>9466897544871</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2186,7 +2162,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2198,15 +2174,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1230591513501</v>
+        <v>5940023404716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2221,7 +2197,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2237,11 +2213,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4749470651030</v>
+        <v>2350060101788</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2256,7 +2232,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2268,15 +2244,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5327123197532</v>
+        <v>5967254023587</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2284,10 +2260,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2043.pdf</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2303,11 +2283,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6427847841811</v>
+        <v>9433382944592</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2322,7 +2302,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2334,11 +2314,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5554714254640</v>
+        <v>8212731136998</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2350,14 +2330,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2045.pdf</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2369,15 +2345,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8490943567226</v>
+        <v>1811212632119</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2392,7 +2368,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2404,15 +2380,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4904719933178</v>
+        <v>6273360667325</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2427,7 +2403,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2439,15 +2415,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5835814896307</v>
+        <v>6185953262866</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2462,7 +2438,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2474,11 +2450,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1067331036573</v>
+        <v>3076073505989</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2509,15 +2485,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9514284645910</v>
+        <v>9609032781936</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2525,14 +2501,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2050.pdf</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2544,15 +2516,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3050043884105</v>
+        <v>6237907473535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2560,14 +2532,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2051.pdf</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2579,15 +2547,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9215430246676</v>
+        <v>8662899622531</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2595,14 +2563,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2052.pdf</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -2614,15 +2578,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1136031973805</v>
+        <v>6976502664436</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2630,14 +2594,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2053.pdf</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2649,11 +2609,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3340641419007</v>
+        <v>5909990427531</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2680,11 +2640,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5913382371158</v>
+        <v>1144232509617</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2696,10 +2656,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2055.pdf</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2711,11 +2675,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5685448258401</v>
+        <v>9612122608765</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2727,7 +2691,11 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2056.pdf</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -2742,15 +2710,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3195125652427</v>
+        <v>9457575059594</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2765,7 +2733,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2777,15 +2745,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7505025821971</v>
+        <v>1608945615480</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2800,7 +2768,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -2812,11 +2780,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8571767709710</v>
+        <v>6660337883540</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2847,15 +2815,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9857812487029</v>
+        <v>1358585173061</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2870,7 +2838,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -2882,11 +2850,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6952199937048</v>
+        <v>4460676990096</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2905,7 +2873,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2917,11 +2885,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2464717434805</v>
+        <v>1118752964344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2940,7 +2908,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -2952,11 +2920,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4853277110507</v>
+        <v>8548543601755</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2968,7 +2936,11 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2063.pdf</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Unmapped_FR</t>
@@ -2983,15 +2955,15 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6474753320680</v>
+        <v>2798987588224</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3006,7 +2978,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3018,11 +2990,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2160350363282</v>
+        <v>8820798978127</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3034,11 +3006,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2065.pdf</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>Kleje</t>
@@ -3053,11 +3021,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5927072229357</v>
+        <v>1717128708086</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3088,15 +3056,15 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8323399627172</v>
+        <v>1007886456557</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3104,14 +3072,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2067.pdf</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3123,11 +3087,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1809087148637</v>
+        <v>8195909027188</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3158,11 +3122,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2723130111648</v>
+        <v>8069097541818</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3181,7 +3145,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3193,15 +3157,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8446949691121</v>
+        <v>4340457110740</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3228,11 +3192,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8740893454427</v>
+        <v>5350378158721</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3263,15 +3227,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2688118934900</v>
+        <v>4343274450902</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3279,10 +3243,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2072.pdf</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3294,15 +3262,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8464260157531</v>
+        <v>4342492372290</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3317,7 +3285,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3329,11 +3297,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5930030504103</v>
+        <v>9769521691971</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -3345,14 +3313,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2074.pdf</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3364,15 +3328,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2504852477662</v>
+        <v>3331295132359</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3380,14 +3344,10 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2075.pdf</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3399,11 +3359,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7603388086981</v>
+        <v>4982197492303</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3434,11 +3394,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5287154460207</v>
+        <v>3079630341290</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3457,7 +3417,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3469,15 +3429,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5243323466939</v>
+        <v>1116914064998</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3492,7 +3452,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3504,11 +3464,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5621404241474</v>
+        <v>7810015083796</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3520,11 +3480,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>https://selena.com/msds/SEL-2079.pdf</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Uszczelniacze</t>
@@ -3539,11 +3495,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5055419624749</v>
+        <v>4118900358922</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3578,7 +3534,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3889017888037</v>
+        <v>8352842480200</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3609,15 +3565,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6476444511735</v>
+        <v>4455516230427</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3632,7 +3588,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3644,15 +3600,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9084000269773</v>
+        <v>9245761658309</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3667,7 +3623,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
     </row>
@@ -3679,15 +3635,15 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>9497169064800</v>
+        <v>5448681092954</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3695,10 +3651,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2084.pdf</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3710,15 +3670,15 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1880306093083</v>
+        <v>8253395253633</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3733,7 +3693,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
@@ -3745,15 +3705,15 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3043721533278</v>
+        <v>7364474601211</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3768,7 +3728,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
     </row>
@@ -3780,11 +3740,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5284960962960</v>
+        <v>2553892922438</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3815,11 +3775,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3549807686591</v>
+        <v>2741448304732</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3838,7 +3798,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
     </row>
@@ -3850,15 +3810,15 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4238586979848</v>
+        <v>6431402736880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3866,10 +3826,14 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://selena.com/msds/SEL-2089.pdf</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
     </row>
